--- a/feature/complement-spec-regulateurs/ig/StructureDefinition-FrPractitionerAgregateur.xlsx
+++ b/feature/complement-spec-regulateurs/ig/StructureDefinition-FrPractitionerAgregateur.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T07:55:27+00:00</t>
+    <t>2026-09-16T16:05:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
